--- a/data/Spring2026/Thesis/Figure 6/all 21 networks stacked bar chart (3 gene 4edge).xlsx
+++ b/data/Spring2026/Thesis/Figure 6/all 21 networks stacked bar chart (3 gene 4edge).xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{68661059-C7A2-4618-9677-1A5A71AA4092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2052" yWindow="1284" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{801D684F-A6E8-40E4-A00F-56C7510AE6D3}"/>
+    <workbookView minimized="1" xWindow="2052" yWindow="1284" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{801D684F-A6E8-40E4-A00F-56C7510AE6D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Stacked" sheetId="2" r:id="rId1"/>

--- a/data/Spring2026/Thesis/Figure 6/all 21 networks stacked bar chart (3 gene 4edge).xlsx
+++ b/data/Spring2026/Thesis/Figure 6/all 21 networks stacked bar chart (3 gene 4edge).xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{68661059-C7A2-4618-9677-1A5A71AA4092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2052" yWindow="1284" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{801D684F-A6E8-40E4-A00F-56C7510AE6D3}"/>
+    <workbookView xWindow="2052" yWindow="1284" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{801D684F-A6E8-40E4-A00F-56C7510AE6D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Stacked" sheetId="2" r:id="rId1"/>
